--- a/Mantenimiento/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1731,11 +1611,6 @@
       </c>
       <c r="K25" t="n">
         <v>2</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>REINA DE LOS ANGELES DE MANCHAY</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.09486</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.8848</v>
-      </c>
-      <c r="I2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.09486</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.8848</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>653</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.11151</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.87503</v>
-      </c>
-      <c r="I3" t="n">
-        <v>226</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.11151</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.87503</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>667</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.09988</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.87475999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>357</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.09988</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.87476</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.12297</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.87164</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1072</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.12297</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.87164</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.22828</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.85886000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>726</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.22828</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.85886</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>6007</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.22942</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.85912</v>
-      </c>
-      <c r="I7" t="n">
-        <v>819</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.22942</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.85912</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>ISAIAS ARDILES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.22935</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.85760999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1039</v>
-      </c>
-      <c r="J8" t="n">
-        <v>56</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.22935</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.85761</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>672</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.09551</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.88687</v>
-      </c>
-      <c r="I9" t="n">
-        <v>265</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.09551</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.88687</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.1116</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.86699</v>
-      </c>
-      <c r="I10" t="n">
-        <v>419</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.1116</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.86699</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>MONITOR HUASCAR</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.11681</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.87108000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>643</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.11681</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.87108</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.12471</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.87635</v>
-      </c>
-      <c r="I12" t="n">
-        <v>93</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.12471</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.87635</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>SAN LORENZO DE MANCHAY</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.10053</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.87981000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>275</v>
-      </c>
-      <c r="J13" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.10053</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.87981</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>SAN ISIDRO DE MANCHAY</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.11482</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.87412999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>869</v>
-      </c>
-      <c r="J14" t="n">
-        <v>48</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.11482</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.87413</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>SANTA ROSA DE LA MESETA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.10706</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.86060999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>42</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.10706</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.86061</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>SANTISIMO JESUS SALVADOR</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.23154</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.85905</v>
-      </c>
-      <c r="I16" t="n">
-        <v>210</v>
-      </c>
-      <c r="J16" t="n">
-        <v>12</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.23154</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.85905</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>EL UNIVERSO DE CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.08358</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.87940999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>291</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.08358</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.87941</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>SAN JOSE DE MANCHAY</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.09941</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.87729</v>
-      </c>
-      <c r="I18" t="n">
-        <v>107</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.09941</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.87729</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.10978</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.86221999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>108</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.10978</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.86222</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>MADRE NICOLETTA GATTI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.22374</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.84672999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>38</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.22374</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.84673</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>SINAI</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.08738</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.87336000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>348</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.08738</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.87336</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.22641</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.85921</v>
-      </c>
-      <c r="I22" t="n">
-        <v>429</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.22641</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.85921</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>TRINITY SCHOOL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.20003</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.87403999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>103</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.20003</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.87404</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>LICEO SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.12702</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.87322</v>
-      </c>
-      <c r="I24" t="n">
-        <v>367</v>
-      </c>
-      <c r="J24" t="n">
-        <v>35</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.12702</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.87322</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>DIVER HOUSE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.10362</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.8753</v>
-      </c>
-      <c r="I25" t="n">
-        <v>36</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.10362</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.8753</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
   </sheetData>
